--- a/docs/Setup Checklist.xlsx
+++ b/docs/Setup Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/12c02f894e99c4a6/Documents/Intern/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="8_{6F8DA544-56B6-4ADF-B5B6-69326FE2747F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91C3E383-58AF-451E-9BD5-0A252EFE8882}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="8_{6F8DA544-56B6-4ADF-B5B6-69326FE2747F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69F9A7F8-D5BA-40FC-A94B-5DB8D952DF38}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="160">
   <si>
     <t>Lab and Tool Setup Checklist</t>
   </si>
@@ -487,13 +487,34 @@
   <si>
     <t>Requested: 6/10/2026
 Expected: 9/10/2026</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Requested: 09/10/2026</t>
+  </si>
+  <si>
+    <t>Requested: 09/10/2027</t>
+  </si>
+  <si>
+    <t>09/10/2026 - Nested Virtualisation still need to be confirmed (I have asked Deakin IT team)</t>
+  </si>
+  <si>
+    <t>Blocked</t>
+  </si>
+  <si>
+    <t>09/10/2026 - Waiting for approval</t>
+  </si>
+  <si>
+    <t>09/10/2026 - Python and pytest are installed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -565,6 +586,12 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -663,7 +690,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -684,17 +711,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -702,15 +718,35 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -718,7 +754,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -730,6 +766,27 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1042,24 +1099,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" x14ac:dyDescent="0.75">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
@@ -1085,331 +1142,339 @@
       <c r="A5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C5" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E5" s="22">
+        <v>46304</v>
+      </c>
+      <c r="F5" s="11"/>
+    </row>
+    <row r="6" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="C6" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A7" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="7"/>
+      <c r="F7" s="11"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" s="16"/>
+      <c r="B8" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" s="10"/>
-      <c r="B8" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="11"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="C9" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="11" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="C10" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="11"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A11" s="10"/>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="16"/>
+      <c r="B11" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="C11" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="C12" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="11"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A13" s="10"/>
-      <c r="B13" s="2" t="s">
+      <c r="A13" s="16"/>
+      <c r="B13" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="C13" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="11"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="C14" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="11"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A15" s="10"/>
-      <c r="B15" s="2" t="s">
+      <c r="A15" s="16"/>
+      <c r="B15" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="C15" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="11"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="C16" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="11"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A17" s="10"/>
-      <c r="B17" s="2" t="s">
+      <c r="A17" s="16"/>
+      <c r="B17" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="2" t="s">
+      <c r="C17" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="11"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="2" t="s">
+      <c r="C18" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="E18" s="7"/>
+      <c r="F18" s="11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A19" s="16"/>
+      <c r="B19" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A19" s="10"/>
-      <c r="B19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="7"/>
+      <c r="F19" s="11"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A20" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A20" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="7"/>
+      <c r="F20" s="11"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A21" s="16"/>
+      <c r="B21" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A21" s="10"/>
-      <c r="B21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="2" t="s">
+      <c r="E21" s="7"/>
+      <c r="F21" s="11"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A22" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A22" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="7"/>
+      <c r="F22" s="11"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A23" s="17"/>
+      <c r="B23" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A23" s="9"/>
-      <c r="B23" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="7"/>
+      <c r="F23" s="11"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A24" s="17"/>
+      <c r="B24" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A24" s="9"/>
-      <c r="B24" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="7"/>
+      <c r="F24" s="11"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A25" s="17"/>
+      <c r="B25" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A25" s="9"/>
-      <c r="B25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D25" s="2" t="s">
+      <c r="E25" s="7"/>
+      <c r="F25" s="11"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A26" s="16"/>
+      <c r="B26" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A26" s="10"/>
-      <c r="B26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:F26" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1426,10 +1491,19 @@
     <mergeCell ref="A20:A21"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D26">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+      <formula>"In progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"Completed"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="4">
       <formula>D5="Completed"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="0" priority="5">
       <formula>D5="Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1459,13 +1533,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
@@ -1477,7 +1551,7 @@
       <c r="C2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="10" t="s">
         <v>142</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -1485,7 +1559,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="15" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -1494,7 +1568,7 @@
       <c r="C3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="8" t="s">
         <v>41</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -1502,14 +1576,14 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" s="9"/>
+      <c r="A4" s="17"/>
       <c r="B4" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E4" s="4" t="s">
@@ -1517,14 +1591,14 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A5" s="9"/>
+      <c r="A5" s="17"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="8" t="s">
         <v>48</v>
       </c>
       <c r="E5" s="4" t="s">
@@ -1532,14 +1606,14 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A6" s="10"/>
+      <c r="A6" s="16"/>
       <c r="B6" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="8" t="s">
         <v>51</v>
       </c>
       <c r="E6" s="4" t="s">
@@ -1547,7 +1621,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="15" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -1556,7 +1630,7 @@
       <c r="C7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -1564,14 +1638,14 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A8" s="9"/>
+      <c r="A8" s="17"/>
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="8" t="s">
         <v>56</v>
       </c>
       <c r="E8" s="4" t="s">
@@ -1579,14 +1653,14 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A9" s="9"/>
+      <c r="A9" s="17"/>
       <c r="B9" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="8" t="s">
         <v>59</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -1594,14 +1668,14 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A10" s="9"/>
+      <c r="A10" s="17"/>
       <c r="B10" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="8" t="s">
         <v>62</v>
       </c>
       <c r="E10" s="4" t="s">
@@ -1609,14 +1683,14 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A11" s="10"/>
+      <c r="A11" s="16"/>
       <c r="B11" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="8" t="s">
         <v>65</v>
       </c>
       <c r="E11" s="3" t="s">
@@ -1624,7 +1698,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="15" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -1633,7 +1707,7 @@
       <c r="C12" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="8" t="s">
         <v>68</v>
       </c>
       <c r="E12" s="3" t="s">
@@ -1641,14 +1715,14 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A13" s="9"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="8" t="s">
         <v>71</v>
       </c>
       <c r="E13" s="4" t="s">
@@ -1656,14 +1730,14 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A14" s="10"/>
+      <c r="A14" s="16"/>
       <c r="B14" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="8" t="s">
         <v>74</v>
       </c>
       <c r="E14" s="4" t="s">
@@ -1671,7 +1745,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="15" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -1680,7 +1754,7 @@
       <c r="C15" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="8" t="s">
         <v>77</v>
       </c>
       <c r="E15" s="4" t="s">
@@ -1688,14 +1762,14 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A16" s="9"/>
+      <c r="A16" s="17"/>
       <c r="B16" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="8" t="s">
         <v>80</v>
       </c>
       <c r="E16" s="4" t="s">
@@ -1703,14 +1777,14 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A17" s="9"/>
+      <c r="A17" s="17"/>
       <c r="B17" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="8" t="s">
         <v>83</v>
       </c>
       <c r="E17" s="4" t="s">
@@ -1718,14 +1792,14 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A18" s="9"/>
+      <c r="A18" s="17"/>
       <c r="B18" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="8" t="s">
         <v>86</v>
       </c>
       <c r="E18" s="3" t="s">
@@ -1733,14 +1807,14 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A19" s="10"/>
+      <c r="A19" s="16"/>
       <c r="B19" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="8" t="s">
         <v>89</v>
       </c>
       <c r="E19" s="4" t="s">
@@ -1748,7 +1822,7 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="15" t="s">
         <v>23</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -1757,7 +1831,7 @@
       <c r="C20" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="8" t="s">
         <v>92</v>
       </c>
       <c r="E20" s="4" t="s">
@@ -1765,14 +1839,14 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A21" s="9"/>
+      <c r="A21" s="17"/>
       <c r="B21" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="8" t="s">
         <v>95</v>
       </c>
       <c r="E21" s="4" t="s">
@@ -1780,14 +1854,14 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A22" s="9"/>
+      <c r="A22" s="17"/>
       <c r="B22" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="8" t="s">
         <v>98</v>
       </c>
       <c r="E22" s="3" t="s">
@@ -1795,14 +1869,14 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A23" s="9"/>
+      <c r="A23" s="17"/>
       <c r="B23" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="8" t="s">
         <v>101</v>
       </c>
       <c r="E23" s="3" t="s">
@@ -1810,14 +1884,14 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A24" s="10"/>
+      <c r="A24" s="16"/>
       <c r="B24" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D24" s="8" t="s">
         <v>104</v>
       </c>
       <c r="E24" s="4" t="s">
@@ -1825,7 +1899,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="15" t="s">
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -1834,7 +1908,7 @@
       <c r="C25" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="8" t="s">
         <v>107</v>
       </c>
       <c r="E25" s="3" t="s">
@@ -1842,14 +1916,14 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A26" s="9"/>
+      <c r="A26" s="17"/>
       <c r="B26" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D26" s="8" t="s">
         <v>110</v>
       </c>
       <c r="E26" s="3" t="s">
@@ -1857,14 +1931,14 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A27" s="10"/>
+      <c r="A27" s="16"/>
       <c r="B27" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="8" t="s">
         <v>113</v>
       </c>
       <c r="E27" s="4" t="s">
@@ -1872,7 +1946,7 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="15" t="s">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -1881,7 +1955,7 @@
       <c r="C28" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D28" s="8" t="s">
         <v>116</v>
       </c>
       <c r="E28" s="3" t="s">
@@ -1889,14 +1963,14 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A29" s="10"/>
+      <c r="A29" s="16"/>
       <c r="B29" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="8" t="s">
         <v>119</v>
       </c>
       <c r="E29" s="4" t="s">
@@ -1904,7 +1978,7 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="15" t="s">
         <v>30</v>
       </c>
       <c r="B30" s="2" t="s">
@@ -1913,7 +1987,7 @@
       <c r="C30" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="9" t="s">
         <v>141</v>
       </c>
       <c r="E30" s="3" t="s">
@@ -1921,14 +1995,14 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A31" s="10"/>
+      <c r="A31" s="16"/>
       <c r="B31" s="2" t="s">
         <v>122</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="8" t="s">
         <v>124</v>
       </c>
       <c r="E31" s="4" t="s">
@@ -1938,15 +2012,15 @@
   </sheetData>
   <autoFilter ref="A2:E31" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="9">
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A3:A6"/>
     <mergeCell ref="A7:A11"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="A15:A19"/>
-    <mergeCell ref="A20:A24"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D4" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
@@ -1991,11 +2065,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" x14ac:dyDescent="0.75">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="5" t="s">
@@ -2009,74 +2083,83 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A5" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="20"/>
-    </row>
-    <row r="5" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A5" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="B6" s="20" t="s">
+      <c r="C9" s="11"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A10" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="20"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="20"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="20"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="20"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A10" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="20"/>
+      <c r="C10" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" sqref="B4:B10" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Not Started,In Progress,Completed,Blocked"</formula1>
@@ -2095,12 +2178,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" x14ac:dyDescent="0.75">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="6" t="s">

--- a/docs/Setup Checklist.xlsx
+++ b/docs/Setup Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/12c02f894e99c4a6/Documents/Intern/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="8_{6F8DA544-56B6-4ADF-B5B6-69326FE2747F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69F9A7F8-D5BA-40FC-A94B-5DB8D952DF38}"/>
+  <xr:revisionPtr revIDLastSave="104" documentId="8_{6F8DA544-56B6-4ADF-B5B6-69326FE2747F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC34F271-4EFB-4B3A-80E3-3AC29DA83BB3}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="Notes" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lab Tool Checklist'!$A$4:$F$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lab Tool Checklist'!$A$4:$F$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tool Resources'!$A$2:$E$31</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="162">
   <si>
     <t>Lab and Tool Setup Checklist</t>
   </si>
@@ -72,9 +72,6 @@
   </si>
   <si>
     <t>Telemetry</t>
-  </si>
-  <si>
-    <t>Sysmon, auditd (if using Ubuntu), Elastic/Wazuh; confirm telemetry works</t>
   </si>
   <si>
     <t>Winlogbeat</t>
@@ -498,9 +495,6 @@
     <t>Requested: 09/10/2027</t>
   </si>
   <si>
-    <t>09/10/2026 - Nested Virtualisation still need to be confirmed (I have asked Deakin IT team)</t>
-  </si>
-  <si>
     <t>Blocked</t>
   </si>
   <si>
@@ -508,6 +502,18 @@
   </si>
   <si>
     <t>09/10/2026 - Python and pytest are installed</t>
+  </si>
+  <si>
+    <t>Sysmon, auditd (if using Ubuntu), Wazuh; confirm telemetry works</t>
+  </si>
+  <si>
+    <t>09/10/2026 - Nested Virtualisation still need to be confirmed (have asked IT team)</t>
+  </si>
+  <si>
+    <t>12/10/2026 - New VM requested and provided (with nested virtualisation feature), but unable to connect (still wait for IT team response)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/10/2026 - Wazuh selected as the proposed central monitoring platform. </t>
   </si>
 </sst>
 </file>
@@ -690,7 +696,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -721,6 +727,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -740,13 +758,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1088,7 +1100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -1099,24 +1111,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" x14ac:dyDescent="0.75">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
@@ -1138,51 +1150,53 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>42</v>
+        <v>144</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="E5" s="22">
+        <v>152</v>
+      </c>
+      <c r="E5" s="13">
         <v>46304</v>
       </c>
-      <c r="F5" s="11"/>
+      <c r="F5" s="25" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="6" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A6" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>42</v>
+        <v>145</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="11" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="19" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>42</v>
+        <v>146</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>9</v>
@@ -1191,11 +1205,11 @@
       <c r="F7" s="11"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" s="16"/>
+      <c r="A8" s="20"/>
       <c r="B8" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="C8" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>12</v>
       </c>
       <c r="D8" s="11" t="s">
@@ -1209,42 +1223,46 @@
         <v>13</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>42</v>
+        <v>148</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>9</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="11" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A10" s="15" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>42</v>
+        <v>158</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>9</v>
       </c>
       <c r="E10" s="7"/>
-      <c r="F10" s="11"/>
+      <c r="F10" s="25" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A11" s="16"/>
+      <c r="A11" s="19" t="s">
+        <v>16</v>
+      </c>
       <c r="B11" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>9</v>
@@ -1253,14 +1271,12 @@
       <c r="F11" s="11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A12" s="15" t="s">
-        <v>17</v>
-      </c>
+      <c r="A12" s="20"/>
       <c r="B12" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="21" t="s">
-        <v>42</v>
+      <c r="C12" s="14" t="s">
+        <v>12</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>9</v>
@@ -1269,12 +1285,14 @@
       <c r="F12" s="11"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A13" s="16"/>
+      <c r="A13" s="19" t="s">
+        <v>19</v>
+      </c>
       <c r="B13" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>12</v>
+        <v>20</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>9</v>
@@ -1283,14 +1301,12 @@
       <c r="F13" s="11"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A14" s="15" t="s">
-        <v>20</v>
-      </c>
+      <c r="A14" s="20"/>
       <c r="B14" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="21" t="s">
-        <v>42</v>
+      <c r="C14" s="14" t="s">
+        <v>12</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>9</v>
@@ -1299,12 +1315,14 @@
       <c r="F14" s="11"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A15" s="16"/>
+      <c r="A15" s="19" t="s">
+        <v>22</v>
+      </c>
       <c r="B15" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>12</v>
+        <v>23</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>9</v>
@@ -1313,14 +1331,12 @@
       <c r="F15" s="11"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A16" s="15" t="s">
-        <v>23</v>
-      </c>
+      <c r="A16" s="20"/>
       <c r="B16" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>42</v>
+        <v>149</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>12</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>9</v>
@@ -1329,44 +1345,46 @@
       <c r="F16" s="11"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A17" s="16"/>
+      <c r="A17" s="19" t="s">
+        <v>24</v>
+      </c>
       <c r="B17" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="C17" s="23" t="s">
-        <v>12</v>
+      <c r="C17" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="D17" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E17" s="7"/>
+      <c r="F17" s="11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A18" s="20"/>
+      <c r="B18" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="11"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A18" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>139</v>
-      </c>
       <c r="E18" s="7"/>
-      <c r="F18" s="11" t="s">
-        <v>159</v>
-      </c>
+      <c r="F18" s="11"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A19" s="16"/>
+      <c r="A19" s="19" t="s">
+        <v>26</v>
+      </c>
       <c r="B19" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>12</v>
+        <v>27</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>9</v>
@@ -1375,14 +1393,12 @@
       <c r="F19" s="11"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A20" s="15" t="s">
-        <v>27</v>
-      </c>
+      <c r="A20" s="20"/>
       <c r="B20" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="21" t="s">
-        <v>42</v>
+      <c r="C20" s="14" t="s">
+        <v>12</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>9</v>
@@ -1391,12 +1407,14 @@
       <c r="F20" s="11"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A21" s="16"/>
+      <c r="A21" s="19" t="s">
+        <v>29</v>
+      </c>
       <c r="B21" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>12</v>
+        <v>30</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>9</v>
@@ -1405,14 +1423,12 @@
       <c r="F21" s="11"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A22" s="15" t="s">
-        <v>30</v>
-      </c>
+      <c r="A22" s="21"/>
       <c r="B22" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="21" t="s">
-        <v>42</v>
+      <c r="C22" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>9</v>
@@ -1421,12 +1437,12 @@
       <c r="F22" s="11"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A23" s="17"/>
+      <c r="A23" s="21"/>
       <c r="B23" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="21" t="s">
-        <v>42</v>
+      <c r="C23" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>9</v>
@@ -1435,12 +1451,12 @@
       <c r="F23" s="11"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A24" s="17"/>
+      <c r="A24" s="21"/>
       <c r="B24" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="21" t="s">
-        <v>42</v>
+      <c r="C24" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>9</v>
@@ -1449,12 +1465,12 @@
       <c r="F24" s="11"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A25" s="17"/>
+      <c r="A25" s="20"/>
       <c r="B25" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="21" t="s">
-        <v>42</v>
+      <c r="C25" s="14" t="s">
+        <v>12</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>9</v>
@@ -1462,35 +1478,20 @@
       <c r="E25" s="7"/>
       <c r="F25" s="11"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A26" s="16"/>
-      <c r="B26" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" s="7"/>
-      <c r="F26" s="11"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:F26" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <mergeCells count="10">
+  <autoFilter ref="A4:F25" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A22:A26"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A21:A25"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A20"/>
   </mergeCells>
-  <conditionalFormatting sqref="D5:D26">
+  <conditionalFormatting sqref="D5:D25">
     <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"In progress"</formula>
     </cfRule>
@@ -1508,10 +1509,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="C5:C26" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="C5:C25" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Priority,Optional"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D5:D26" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" sqref="D5:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Not Started,In Progress,Completed,Blocked"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1533,477 +1534,477 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
+      <c r="A1" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="D2" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="19" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>41</v>
-      </c>
       <c r="E3" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="21"/>
+      <c r="B4" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" s="17"/>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="21"/>
+      <c r="B5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A5" s="17"/>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="E5" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" s="20"/>
+      <c r="B6" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A6" s="16"/>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="E6" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A7" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="E7" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" s="21"/>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A8" s="17"/>
-      <c r="B8" s="2" t="s">
+      <c r="D8" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" s="21"/>
+      <c r="B9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A10" s="21"/>
+      <c r="B10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A11" s="20"/>
+      <c r="B11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A12" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A9" s="17"/>
-      <c r="B9" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A10" s="17"/>
-      <c r="B10" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A11" s="16"/>
-      <c r="B11" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" s="8" t="s">
+      <c r="B12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A12" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="E12" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A13" s="21"/>
+      <c r="B13" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A13" s="17"/>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="E13" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A14" s="20"/>
+      <c r="B14" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A14" s="16"/>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="E14" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A15" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A15" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="E15" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A16" s="21"/>
+      <c r="B16" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A16" s="17"/>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="E16" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A17" s="21"/>
+      <c r="B17" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A17" s="17"/>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="E17" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A18" s="21"/>
+      <c r="B18" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A18" s="17"/>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="E18" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A19" s="20"/>
+      <c r="B19" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A19" s="16"/>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="E19" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A20" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A20" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="E20" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A21" s="21"/>
+      <c r="B21" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A21" s="17"/>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="E21" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A22" s="21"/>
+      <c r="B22" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A22" s="17"/>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="E22" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A23" s="21"/>
+      <c r="B23" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A23" s="17"/>
-      <c r="B23" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="E23" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A24" s="20"/>
+      <c r="B24" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A24" s="16"/>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="E24" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A25" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A25" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="E25" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A26" s="21"/>
+      <c r="B26" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A26" s="17"/>
-      <c r="B26" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="E26" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A27" s="20"/>
+      <c r="B27" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A27" s="16"/>
-      <c r="B27" s="2" t="s">
+      <c r="C27" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="E27" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A28" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A28" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="s">
+      <c r="C28" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="E28" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A29" s="20"/>
+      <c r="B29" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A29" s="16"/>
-      <c r="B29" s="2" t="s">
+      <c r="C29" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="E29" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A30" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A30" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="2" t="s">
+      <c r="C30" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A31" s="20"/>
+      <c r="B31" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D30" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A31" s="16"/>
-      <c r="B31" s="2" t="s">
+      <c r="C31" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="8" t="s">
         <v>123</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>124</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>12</v>
@@ -2065,15 +2066,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" x14ac:dyDescent="0.75">
-      <c r="A1" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
+      <c r="A1" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>5</v>
@@ -2084,62 +2085,62 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A5" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>9</v>
@@ -2148,7 +2149,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>9</v>
@@ -2178,46 +2179,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" x14ac:dyDescent="0.75">
-      <c r="A1" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
+      <c r="A1" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
